--- a/source/LTU/TD_LTUv5_Restructure.xlsx
+++ b/source/LTU/TD_LTUv5_Restructure.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Trait" sheetId="1" state="visible" r:id="rId3"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="294">
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -102,6 +102,9 @@
   </si>
   <si>
     <t xml:space="preserve">plant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">any plant</t>
   </si>
   <si>
     <t xml:space="preserve">overall stature</t>
@@ -1838,7 +1841,7 @@
         <v>25</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -1890,36 +1893,36 @@
     </row>
     <row r="3" s="23" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>25</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M3" s="1"/>
       <c r="N3" s="6"/>
@@ -1945,25 +1948,25 @@
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="I4" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M4" s="1"/>
       <c r="O4" s="24"/>
@@ -2003,28 +2006,28 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>33</v>
-      </c>
       <c r="K5" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M5" s="1"/>
       <c r="O5" s="24"/>
@@ -2064,28 +2067,28 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="I6" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M6" s="1"/>
       <c r="O6" s="24"/>
@@ -2125,28 +2128,28 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="I7" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M7" s="1"/>
       <c r="O7" s="24"/>
@@ -2186,28 +2189,28 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="I8" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M8" s="1"/>
       <c r="O8" s="24"/>
@@ -2247,28 +2250,28 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="I9" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M9" s="1"/>
       <c r="O9" s="24"/>
@@ -2308,28 +2311,28 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="I10" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M10" s="1"/>
       <c r="O10" s="24"/>
@@ -2369,28 +2372,28 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="I11" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M11" s="1"/>
       <c r="O11" s="24"/>
@@ -2430,28 +2433,28 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="I12" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M12" s="1"/>
       <c r="O12" s="24"/>
@@ -2491,28 +2494,28 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="I13" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M13" s="1"/>
       <c r="O13" s="24"/>
@@ -2552,25 +2555,25 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="G14" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="I14" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M14" s="1"/>
       <c r="O14" s="24"/>
@@ -2610,28 +2613,28 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="I15" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M15" s="1"/>
       <c r="O15" s="24"/>
@@ -2671,31 +2674,31 @@
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="F16" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="I16" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M16" s="1"/>
       <c r="O16" s="24"/>
@@ -2735,31 +2738,31 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="I17" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M17" s="1"/>
       <c r="O17" s="24"/>
@@ -2799,31 +2802,31 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="I18" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M18" s="1"/>
       <c r="O18" s="24"/>
@@ -2863,31 +2866,31 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="I19" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M19" s="1"/>
       <c r="O19" s="24"/>
@@ -2927,28 +2930,28 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H20" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="I20" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>25</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M20" s="1"/>
       <c r="O20" s="24"/>
@@ -2988,31 +2991,31 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="J21" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M21" s="1"/>
       <c r="O21" s="24"/>
@@ -3052,28 +3055,28 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>99</v>
-      </c>
       <c r="I22" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M22" s="1"/>
       <c r="O22" s="24"/>
@@ -3113,28 +3116,28 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M23" s="1"/>
       <c r="O23" s="24"/>
@@ -3174,31 +3177,31 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="I24" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M24" s="1"/>
       <c r="O24" s="24"/>
@@ -3238,31 +3241,31 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>113</v>
-      </c>
       <c r="E25" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M25" s="1"/>
       <c r="O25" s="24"/>
@@ -3302,28 +3305,28 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>116</v>
-      </c>
       <c r="J26" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M26" s="1"/>
       <c r="O26" s="24"/>
@@ -3363,28 +3366,28 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J27" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>120</v>
-      </c>
       <c r="K27" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M27" s="1"/>
       <c r="O27" s="24"/>
@@ -3424,34 +3427,34 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H28" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>124</v>
-      </c>
       <c r="I28" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M28" s="1"/>
       <c r="O28" s="24"/>
@@ -3491,31 +3494,31 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>129</v>
-      </c>
       <c r="I29" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M29" s="1"/>
       <c r="O29" s="24"/>
@@ -3555,34 +3558,34 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>134</v>
-      </c>
       <c r="F30" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M30" s="1"/>
       <c r="O30" s="24"/>
@@ -3622,28 +3625,28 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>139</v>
-      </c>
       <c r="G31" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M31" s="1"/>
       <c r="O31" s="24"/>
@@ -3683,52 +3686,52 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H32" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="F32" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>141</v>
-      </c>
       <c r="I32" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>25</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O32" s="25" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P32" s="25" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q32" s="25" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="R32" s="25" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="S32" s="25" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="T32" s="26"/>
       <c r="U32" s="26"/>
@@ -3761,49 +3764,49 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>153</v>
-      </c>
       <c r="F33" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J33" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L33" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="K33" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="M33" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O33" s="24" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P33" s="24" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q33" s="24" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="R33" s="24"/>
       <c r="S33" s="24"/>
@@ -3839,34 +3842,34 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H34" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="I34" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>25</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M34" s="1"/>
       <c r="O34" s="25"/>
@@ -3905,43 +3908,43 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H35" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="I35" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>25</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M35" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="N35" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="N35" s="1" t="s">
-        <v>172</v>
-      </c>
       <c r="O35" s="25" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P35" s="25"/>
       <c r="Q35" s="25"/>
@@ -3978,40 +3981,40 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H36" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>175</v>
-      </c>
       <c r="I36" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>25</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N36" s="27" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O36" s="25"/>
       <c r="P36" s="25"/>
@@ -4049,28 +4052,28 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B37" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H37" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="F37" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>182</v>
-      </c>
       <c r="I37" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M37" s="1"/>
       <c r="O37" s="25"/>
@@ -4109,28 +4112,28 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H38" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="F38" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>185</v>
-      </c>
       <c r="I38" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>25</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M38" s="1"/>
       <c r="O38" s="25"/>
@@ -4169,28 +4172,28 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B39" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H39" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>189</v>
-      </c>
       <c r="I39" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M39" s="1"/>
       <c r="O39" s="25"/>
@@ -4525,11 +4528,11 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="32" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B2" s="32"/>
       <c r="C2" s="32" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D2" s="32"/>
       <c r="E2" s="32"/>
@@ -4540,16 +4543,16 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="32" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B3" s="32" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D3" s="32" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E3" s="32"/>
       <c r="F3" s="32"/>
@@ -4559,16 +4562,16 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="32" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E4" s="32"/>
       <c r="F4" s="32"/>
@@ -4578,16 +4581,16 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="32" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E5" s="32"/>
       <c r="F5" s="32"/>
@@ -4601,12 +4604,12 @@
       </c>
       <c r="B6" s="32"/>
       <c r="C6" s="32" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D6" s="32"/>
       <c r="E6" s="32"/>
       <c r="F6" s="32" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>24</v>
@@ -4614,11 +4617,11 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7" s="32"/>
       <c r="C7" s="32" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D7" s="32"/>
       <c r="E7" s="32"/>
@@ -4629,11 +4632,11 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="32" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B8" s="32"/>
       <c r="C8" s="32" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D8" s="32"/>
       <c r="E8" s="32"/>
@@ -4644,11 +4647,11 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="32" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" s="32"/>
       <c r="C9" s="32" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D9" s="32"/>
       <c r="E9" s="32"/>
@@ -4659,11 +4662,11 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B10" s="32"/>
       <c r="C10" s="32" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="32"/>
@@ -4674,11 +4677,11 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="32" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B11" s="32"/>
       <c r="C11" s="32" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D11" s="32"/>
       <c r="E11" s="32"/>
@@ -4689,11 +4692,11 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B12" s="32"/>
       <c r="C12" s="32" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D12" s="32"/>
       <c r="E12" s="32"/>
@@ -4704,11 +4707,11 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B13" s="32"/>
       <c r="C13" s="32" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D13" s="32"/>
       <c r="E13" s="32"/>
@@ -4719,11 +4722,11 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B14" s="32"/>
       <c r="C14" s="32" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D14" s="32"/>
       <c r="E14" s="32"/>
@@ -4734,11 +4737,11 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="32" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B15" s="32"/>
       <c r="C15" s="32" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D15" s="32"/>
       <c r="E15" s="32"/>
@@ -4749,11 +4752,11 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="32" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B16" s="32"/>
       <c r="C16" s="32" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="32"/>
@@ -4764,11 +4767,11 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="32" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B17" s="32"/>
       <c r="C17" s="32" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D17" s="32"/>
       <c r="E17" s="32"/>
@@ -4779,11 +4782,11 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="32" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B18" s="32"/>
       <c r="C18" s="32" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D18" s="32"/>
       <c r="E18" s="32"/>
@@ -4794,11 +4797,11 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B19" s="32"/>
       <c r="C19" s="32" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D19" s="32"/>
       <c r="E19" s="32"/>
@@ -4809,11 +4812,11 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="32" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B20" s="32"/>
       <c r="C20" s="32" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D20" s="32"/>
       <c r="E20" s="32"/>
@@ -4824,11 +4827,11 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="32" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B21" s="32"/>
       <c r="C21" s="32" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D21" s="32"/>
       <c r="E21" s="32"/>
@@ -4839,11 +4842,11 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="32" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B22" s="32"/>
       <c r="C22" s="32" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D22" s="32"/>
       <c r="E22" s="32"/>
@@ -4854,11 +4857,11 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="32" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B23" s="32"/>
       <c r="C23" s="32" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D23" s="32"/>
       <c r="E23" s="32"/>
@@ -4869,13 +4872,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="32" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B24" s="32" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C24" s="32" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D24" s="32"/>
       <c r="E24" s="32"/>
@@ -4886,13 +4889,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="32" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B25" s="32" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C25" s="32" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D25" s="32"/>
       <c r="E25" s="32"/>
@@ -4903,11 +4906,11 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="32" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D26" s="32"/>
       <c r="E26" s="32"/>
@@ -4918,13 +4921,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="32" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B27" s="32" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C27" s="32" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D27" s="32"/>
       <c r="E27" s="32"/>
@@ -4935,11 +4938,11 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="32" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B28" s="32"/>
       <c r="C28" s="32" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D28" s="32"/>
       <c r="E28" s="32"/>
@@ -5096,17 +5099,17 @@
     <tabColor rgb="FF800080"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr defaultColWidth="9.34375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="42.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="89.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="32.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="30.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="31.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="17.33"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="9.34"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="34" width="9.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="2" width="32.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="30.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="31.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="17.33"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="9.34"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="34" width="9.34"/>
   </cols>
   <sheetData>
     <row r="1" s="39" customFormat="true" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5116,445 +5119,448 @@
       <c r="B1" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="C1" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="E1" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="36" t="s">
+      <c r="F1" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="37" t="s">
+      <c r="G1" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="F2" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="F3" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="F4" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="F5" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="F6" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="F7" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="F8" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="F9" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="F10" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="F11" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="F12" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="F13" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="F14" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="F15" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="F16" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="F17" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="F18" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="F19" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="F20" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="F21" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="F22" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="F23" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="F24" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="F25" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="G25" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="F26" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G26" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="F27" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="G27" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="F28" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="G28" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="F29" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="G29" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="F30" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="F31" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="G31" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="F32" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="G32" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="F33" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="G33" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="F34" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="G34" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="F35" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="G35" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="F36" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="G36" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="F37" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="G37" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="F38" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="G38" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="F39" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="G39" s="2" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F1" type="none">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G1" type="none">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F2:F1039" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G2:G1039" type="list">
       <formula1>#ref!</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5575,16 +5581,16 @@
     <tabColor rgb="FF158466"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultColWidth="9.34375" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="16.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="4" width="73.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="4" width="28.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="4" width="29.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="4" width="29.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="4" width="17.33"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="4" width="9.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="4" width="28.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="4" width="29.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="4" width="29.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="4" width="17.33"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="4" width="9.34"/>
   </cols>
   <sheetData>
     <row r="1" s="40" customFormat="true" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5595,15 +5601,18 @@
         <v>1</v>
       </c>
       <c r="C1" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="E1" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="40" t="s">
+      <c r="F1" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="G1" s="13" t="s">
         <v>6</v>
       </c>
     </row>
@@ -5612,107 +5621,107 @@
         <v>25</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="F2" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="F3" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="F4" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="F5" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="F6" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="F7" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="F8" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="F9" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="F10" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F1" type="none">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G1" type="none">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F2:F1010" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G2:G1010" type="list">
       <formula1>#ref!</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5733,17 +5742,17 @@
     <tabColor rgb="FF2A6099"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="9.34375" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="18.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="34.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="5" width="69.4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="5" width="24.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="5" width="30.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="5" width="40.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="5" width="17.33"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="5" width="9.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="5" width="30.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="5" width="40.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="5" width="17.33"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="5" width="9.34"/>
   </cols>
   <sheetData>
     <row r="1" s="41" customFormat="true" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5751,174 +5760,181 @@
         <v>0</v>
       </c>
       <c r="B1" s="41" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C1" s="41" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="41" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E1" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="41" t="s">
+      <c r="G1" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="41" t="s">
+      <c r="H1" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="I1" s="14" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="G2" s="5" t="s">
         <v>269</v>
       </c>
       <c r="H2" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="I2" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>273</v>
+        <v>26</v>
       </c>
       <c r="H3" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="G4" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>278</v>
       </c>
       <c r="H4" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="I4" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="G5" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>283</v>
       </c>
       <c r="H5" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="I5" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="G6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>288</v>
       </c>
       <c r="H6" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="I6" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>292</v>
+        <v>26</v>
       </c>
       <c r="H7" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="I7" s="5" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H1" type="none">
+  <dataValidations count="3">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I1" type="none">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H2:H1007" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I2:I1007" type="list">
       <formula1>#ref!</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D2:D1007" type="list">
+      <formula1>$A$2:$A$10000</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" display="https://en.wikipedia.org/wiki/Plantae"/>
-    <hyperlink ref="G3" r:id="rId2" display="https://en.wikipedia.org/wiki/Poaceae"/>
-    <hyperlink ref="E4" r:id="rId3" display="http://cavoc.org/cvo/ns/2/C2"/>
-    <hyperlink ref="G4" r:id="rId4" display="https://en.wikipedia.org/wiki/Wheat"/>
-    <hyperlink ref="E5" r:id="rId5" display="http://cavoc.org/cvo/ns/2/C259"/>
-    <hyperlink ref="G5" r:id="rId6" display="https://en.wikipedia.org/wiki/Barley"/>
-    <hyperlink ref="E6" r:id="rId7" display="http://cavoc.org/cvo/ns/2/C6"/>
-    <hyperlink ref="G6" r:id="rId8" display="https://en.wikipedia.org/wiki/Tomato"/>
-    <hyperlink ref="G7" r:id="rId9" display="https://en.wikipedia.org/wiki/Cannabis_sativa"/>
+    <hyperlink ref="H2" r:id="rId1" display="https://en.wikipedia.org/wiki/Plantae"/>
+    <hyperlink ref="H3" r:id="rId2" display="https://en.wikipedia.org/wiki/Poaceae"/>
+    <hyperlink ref="F4" r:id="rId3" display="http://cavoc.org/cvo/ns/2/C2"/>
+    <hyperlink ref="H4" r:id="rId4" display="https://en.wikipedia.org/wiki/Wheat"/>
+    <hyperlink ref="F5" r:id="rId5" display="http://cavoc.org/cvo/ns/2/C259"/>
+    <hyperlink ref="H5" r:id="rId6" display="https://en.wikipedia.org/wiki/Barley"/>
+    <hyperlink ref="F6" r:id="rId7" display="http://cavoc.org/cvo/ns/2/C6"/>
+    <hyperlink ref="H6" r:id="rId8" display="https://en.wikipedia.org/wiki/Tomato"/>
+    <hyperlink ref="H7" r:id="rId9" display="https://en.wikipedia.org/wiki/Cannabis_sativa"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
